--- a/专利/德清瓜山水产养殖有限公司/存活率/正式/01-青鱼/07-翘嘴红鲌/养殖翘嘴红鲌存活率检测数据包.xlsx
+++ b/专利/德清瓜山水产养殖有限公司/存活率/正式/01-青鱼/07-翘嘴红鲌/养殖翘嘴红鲌存活率检测数据包.xlsx
@@ -466,7 +466,7 @@
         <v>4420</v>
       </c>
       <c r="F2" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G2">
         <v>156</v>
@@ -516,7 +516,7 @@
         <v>4739</v>
       </c>
       <c r="F3" t="str">
-        <v>疾病</v>
+        <v>疾病-肠炎病</v>
       </c>
       <c r="G3">
         <v>90</v>
@@ -566,7 +566,7 @@
         <v>6488</v>
       </c>
       <c r="F4" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G4">
         <v>121</v>
@@ -616,7 +616,7 @@
         <v>6672</v>
       </c>
       <c r="F5" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G5">
         <v>151</v>
@@ -666,7 +666,7 @@
         <v>6027</v>
       </c>
       <c r="F6" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G6">
         <v>95</v>
@@ -716,7 +716,7 @@
         <v>3942</v>
       </c>
       <c r="F7" t="str">
-        <v>水质异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G7">
         <v>120</v>
@@ -766,7 +766,7 @@
         <v>7394</v>
       </c>
       <c r="F8" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G8">
         <v>115</v>
@@ -816,7 +816,7 @@
         <v>3037</v>
       </c>
       <c r="F9" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G9">
         <v>110</v>
@@ -866,7 +866,7 @@
         <v>7548</v>
       </c>
       <c r="F10" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G10">
         <v>162</v>
@@ -916,7 +916,7 @@
         <v>3446</v>
       </c>
       <c r="F11" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G11">
         <v>160</v>
@@ -966,7 +966,7 @@
         <v>4961</v>
       </c>
       <c r="F12" t="str">
-        <v>水质异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G12">
         <v>114</v>
@@ -1016,7 +1016,7 @@
         <v>6267</v>
       </c>
       <c r="F13" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G13">
         <v>100</v>
@@ -1066,7 +1066,7 @@
         <v>4465</v>
       </c>
       <c r="F14" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G14">
         <v>129</v>
@@ -1116,7 +1116,7 @@
         <v>3424</v>
       </c>
       <c r="F15" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G15">
         <v>125</v>
@@ -1166,7 +1166,7 @@
         <v>6004</v>
       </c>
       <c r="F16" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G16">
         <v>138</v>
@@ -1216,7 +1216,7 @@
         <v>6622</v>
       </c>
       <c r="F17" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G17">
         <v>123</v>
@@ -1266,7 +1266,7 @@
         <v>4559</v>
       </c>
       <c r="F18" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G18">
         <v>166</v>
@@ -1316,7 +1316,7 @@
         <v>7630</v>
       </c>
       <c r="F19" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G19">
         <v>133</v>
@@ -1366,7 +1366,7 @@
         <v>5840</v>
       </c>
       <c r="F20" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G20">
         <v>125</v>
@@ -1416,7 +1416,7 @@
         <v>4035</v>
       </c>
       <c r="F21" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G21">
         <v>180</v>
@@ -1466,7 +1466,7 @@
         <v>3504</v>
       </c>
       <c r="F22" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G22">
         <v>107</v>
@@ -1516,7 +1516,7 @@
         <v>5225</v>
       </c>
       <c r="F23" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G23">
         <v>174</v>
@@ -1566,7 +1566,7 @@
         <v>6625</v>
       </c>
       <c r="F24" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G24">
         <v>105</v>
@@ -1616,7 +1616,7 @@
         <v>5716</v>
       </c>
       <c r="F25" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G25">
         <v>101</v>
@@ -1666,7 +1666,7 @@
         <v>5722</v>
       </c>
       <c r="F26" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G26">
         <v>143</v>
@@ -1716,7 +1716,7 @@
         <v>3135</v>
       </c>
       <c r="F27" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G27">
         <v>108</v>
@@ -1766,7 +1766,7 @@
         <v>6708</v>
       </c>
       <c r="F28" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G28">
         <v>137</v>
@@ -1816,7 +1816,7 @@
         <v>3902</v>
       </c>
       <c r="F29" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G29">
         <v>128</v>
@@ -1866,7 +1866,7 @@
         <v>3352</v>
       </c>
       <c r="F30" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G30">
         <v>148</v>
@@ -1916,7 +1916,7 @@
         <v>5311</v>
       </c>
       <c r="F31" t="str">
-        <v>疾病</v>
+        <v>疾病-指环虫感染</v>
       </c>
       <c r="G31">
         <v>118</v>
@@ -1966,7 +1966,7 @@
         <v>5770</v>
       </c>
       <c r="F32" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G32">
         <v>169</v>
@@ -2016,7 +2016,7 @@
         <v>5827</v>
       </c>
       <c r="F33" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G33">
         <v>140</v>
@@ -2066,7 +2066,7 @@
         <v>4660</v>
       </c>
       <c r="F34" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G34">
         <v>165</v>
@@ -2116,7 +2116,7 @@
         <v>3253</v>
       </c>
       <c r="F35" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G35">
         <v>152</v>
@@ -2166,7 +2166,7 @@
         <v>6160</v>
       </c>
       <c r="F36" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G36">
         <v>92</v>
@@ -2216,7 +2216,7 @@
         <v>4782</v>
       </c>
       <c r="F37" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G37">
         <v>124</v>
@@ -2266,7 +2266,7 @@
         <v>5322</v>
       </c>
       <c r="F38" t="str">
-        <v>疾病</v>
+        <v>疾病-细菌性烂鳃病</v>
       </c>
       <c r="G38">
         <v>139</v>
@@ -2316,7 +2316,7 @@
         <v>6999</v>
       </c>
       <c r="F39" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G39">
         <v>158</v>
@@ -2366,7 +2366,7 @@
         <v>5848</v>
       </c>
       <c r="F40" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G40">
         <v>131</v>
@@ -2416,7 +2416,7 @@
         <v>7115</v>
       </c>
       <c r="F41" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G41">
         <v>93</v>
@@ -2466,7 +2466,7 @@
         <v>3284</v>
       </c>
       <c r="F42" t="str">
-        <v>疾病</v>
+        <v>疾病-指环虫感染</v>
       </c>
       <c r="G42">
         <v>110</v>
@@ -2516,7 +2516,7 @@
         <v>3756</v>
       </c>
       <c r="F43" t="str">
-        <v>疾病</v>
+        <v>疾病-指环虫感染</v>
       </c>
       <c r="G43">
         <v>127</v>
@@ -2566,7 +2566,7 @@
         <v>5421</v>
       </c>
       <c r="F44" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G44">
         <v>152</v>
@@ -2616,7 +2616,7 @@
         <v>7649</v>
       </c>
       <c r="F45" t="str">
-        <v>水质异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G45">
         <v>97</v>
@@ -2666,7 +2666,7 @@
         <v>3854</v>
       </c>
       <c r="F46" t="str">
-        <v>疾病</v>
+        <v>疾病-细菌性烂鳃病</v>
       </c>
       <c r="G46">
         <v>126</v>
@@ -2716,7 +2716,7 @@
         <v>4999</v>
       </c>
       <c r="F47" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G47">
         <v>175</v>
@@ -2766,7 +2766,7 @@
         <v>4962</v>
       </c>
       <c r="F48" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G48">
         <v>108</v>
@@ -2816,7 +2816,7 @@
         <v>3432</v>
       </c>
       <c r="F49" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G49">
         <v>145</v>
@@ -2866,7 +2866,7 @@
         <v>3406</v>
       </c>
       <c r="F50" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G50">
         <v>97</v>
@@ -2916,7 +2916,7 @@
         <v>5730</v>
       </c>
       <c r="F51" t="str">
-        <v>疾病</v>
+        <v>疾病-车轮虫感染</v>
       </c>
       <c r="G51">
         <v>118</v>
@@ -2966,7 +2966,7 @@
         <v>6127</v>
       </c>
       <c r="F52" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G52">
         <v>152</v>
@@ -3016,7 +3016,7 @@
         <v>3332</v>
       </c>
       <c r="F53" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G53">
         <v>157</v>
@@ -3066,7 +3066,7 @@
         <v>3171</v>
       </c>
       <c r="F54" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G54">
         <v>158</v>
@@ -3116,7 +3116,7 @@
         <v>6889</v>
       </c>
       <c r="F55" t="str">
-        <v>水质异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G55">
         <v>164</v>
@@ -3166,7 +3166,7 @@
         <v>7012</v>
       </c>
       <c r="F56" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G56">
         <v>153</v>
@@ -3216,7 +3216,7 @@
         <v>4723</v>
       </c>
       <c r="F57" t="str">
-        <v>疾病</v>
+        <v>疾病-指环虫感染</v>
       </c>
       <c r="G57">
         <v>151</v>
@@ -3266,7 +3266,7 @@
         <v>4030</v>
       </c>
       <c r="F58" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G58">
         <v>176</v>
@@ -3316,7 +3316,7 @@
         <v>4498</v>
       </c>
       <c r="F59" t="str">
-        <v>疾病</v>
+        <v>疾病-水霉病</v>
       </c>
       <c r="G59">
         <v>118</v>
@@ -3366,7 +3366,7 @@
         <v>7651</v>
       </c>
       <c r="F60" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G60">
         <v>157</v>
@@ -3416,7 +3416,7 @@
         <v>3528</v>
       </c>
       <c r="F61" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G61">
         <v>99</v>
@@ -3466,7 +3466,7 @@
         <v>4687</v>
       </c>
       <c r="F62" t="str">
-        <v>水质异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G62">
         <v>93</v>
@@ -3516,7 +3516,7 @@
         <v>5321</v>
       </c>
       <c r="F63" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G63">
         <v>151</v>
@@ -3566,7 +3566,7 @@
         <v>3839</v>
       </c>
       <c r="F64" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G64">
         <v>111</v>
@@ -3616,7 +3616,7 @@
         <v>7537</v>
       </c>
       <c r="F65" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G65">
         <v>128</v>
@@ -3666,7 +3666,7 @@
         <v>4565</v>
       </c>
       <c r="F66" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G66">
         <v>133</v>
@@ -3716,7 +3716,7 @@
         <v>5499</v>
       </c>
       <c r="F67" t="str">
-        <v>水质异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G67">
         <v>118</v>
@@ -3766,7 +3766,7 @@
         <v>5534</v>
       </c>
       <c r="F68" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G68">
         <v>103</v>
@@ -3816,7 +3816,7 @@
         <v>4089</v>
       </c>
       <c r="F69" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G69">
         <v>118</v>
@@ -3866,7 +3866,7 @@
         <v>7132</v>
       </c>
       <c r="F70" t="str">
-        <v>疾病</v>
+        <v>疾病-车轮虫感染</v>
       </c>
       <c r="G70">
         <v>168</v>
@@ -3916,7 +3916,7 @@
         <v>3334</v>
       </c>
       <c r="F71" t="str">
-        <v>疾病</v>
+        <v>疾病-细菌性烂鳃病</v>
       </c>
       <c r="G71">
         <v>143</v>
@@ -3966,7 +3966,7 @@
         <v>3451</v>
       </c>
       <c r="F72" t="str">
-        <v>疾病</v>
+        <v>疾病-车轮虫感染</v>
       </c>
       <c r="G72">
         <v>109</v>
@@ -4016,7 +4016,7 @@
         <v>5447</v>
       </c>
       <c r="F73" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G73">
         <v>123</v>
@@ -4066,7 +4066,7 @@
         <v>5739</v>
       </c>
       <c r="F74" t="str">
-        <v>疾病</v>
+        <v>疾病-肠炎病</v>
       </c>
       <c r="G74">
         <v>121</v>
@@ -4116,7 +4116,7 @@
         <v>4950</v>
       </c>
       <c r="F75" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G75">
         <v>155</v>
@@ -4166,7 +4166,7 @@
         <v>5702</v>
       </c>
       <c r="F76" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G76">
         <v>165</v>
@@ -4216,7 +4216,7 @@
         <v>6700</v>
       </c>
       <c r="F77" t="str">
-        <v>疾病</v>
+        <v>疾病-水霉病</v>
       </c>
       <c r="G77">
         <v>171</v>
@@ -4266,7 +4266,7 @@
         <v>4442</v>
       </c>
       <c r="F78" t="str">
-        <v>疾病</v>
+        <v>疾病-水霉病</v>
       </c>
       <c r="G78">
         <v>93</v>
@@ -4316,7 +4316,7 @@
         <v>5157</v>
       </c>
       <c r="F79" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G79">
         <v>152</v>
@@ -4366,7 +4366,7 @@
         <v>7147</v>
       </c>
       <c r="F80" t="str">
-        <v>疾病</v>
+        <v>疾病-车轮虫感染</v>
       </c>
       <c r="G80">
         <v>143</v>
@@ -4416,7 +4416,7 @@
         <v>3366</v>
       </c>
       <c r="F81" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G81">
         <v>90</v>
@@ -4466,7 +4466,7 @@
         <v>5093</v>
       </c>
       <c r="F82" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G82">
         <v>126</v>
@@ -4516,7 +4516,7 @@
         <v>7387</v>
       </c>
       <c r="F83" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G83">
         <v>126</v>
@@ -4566,7 +4566,7 @@
         <v>6884</v>
       </c>
       <c r="F84" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G84">
         <v>123</v>
@@ -4616,7 +4616,7 @@
         <v>4934</v>
       </c>
       <c r="F85" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G85">
         <v>141</v>
@@ -4666,7 +4666,7 @@
         <v>3730</v>
       </c>
       <c r="F86" t="str">
-        <v>疾病</v>
+        <v>疾病-指环虫感染</v>
       </c>
       <c r="G86">
         <v>116</v>
@@ -4716,7 +4716,7 @@
         <v>6665</v>
       </c>
       <c r="F87" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G87">
         <v>97</v>
@@ -4766,7 +4766,7 @@
         <v>7577</v>
       </c>
       <c r="F88" t="str">
-        <v>水质异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G88">
         <v>104</v>
@@ -4816,7 +4816,7 @@
         <v>4324</v>
       </c>
       <c r="F89" t="str">
-        <v>水质异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G89">
         <v>131</v>
@@ -4866,7 +4866,7 @@
         <v>3083</v>
       </c>
       <c r="F90" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G90">
         <v>117</v>
@@ -4916,7 +4916,7 @@
         <v>7674</v>
       </c>
       <c r="F91" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G91">
         <v>111</v>
@@ -4966,7 +4966,7 @@
         <v>4504</v>
       </c>
       <c r="F92" t="str">
-        <v>疾病</v>
+        <v>疾病-车轮虫感染</v>
       </c>
       <c r="G92">
         <v>161</v>
@@ -5016,7 +5016,7 @@
         <v>5877</v>
       </c>
       <c r="F93" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G93">
         <v>92</v>
@@ -5066,7 +5066,7 @@
         <v>6251</v>
       </c>
       <c r="F94" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G94">
         <v>106</v>
@@ -5116,7 +5116,7 @@
         <v>7473</v>
       </c>
       <c r="F95" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G95">
         <v>93</v>
@@ -5166,7 +5166,7 @@
         <v>4471</v>
       </c>
       <c r="F96" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G96">
         <v>114</v>
@@ -5216,7 +5216,7 @@
         <v>4698</v>
       </c>
       <c r="F97" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G97">
         <v>175</v>
@@ -5266,7 +5266,7 @@
         <v>4018</v>
       </c>
       <c r="F98" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G98">
         <v>114</v>
@@ -5316,7 +5316,7 @@
         <v>3528</v>
       </c>
       <c r="F99" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G99">
         <v>170</v>
@@ -5366,7 +5366,7 @@
         <v>6405</v>
       </c>
       <c r="F100" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G100">
         <v>101</v>
@@ -5416,7 +5416,7 @@
         <v>5330</v>
       </c>
       <c r="F101" t="str">
-        <v>疾病</v>
+        <v>疾病-肠炎病</v>
       </c>
       <c r="G101">
         <v>177</v>
@@ -5466,7 +5466,7 @@
         <v>5265</v>
       </c>
       <c r="F102" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G102">
         <v>120</v>
@@ -5516,7 +5516,7 @@
         <v>7358</v>
       </c>
       <c r="F103" t="str">
-        <v>疾病</v>
+        <v>疾病-指环虫感染</v>
       </c>
       <c r="G103">
         <v>111</v>
@@ -5566,7 +5566,7 @@
         <v>3738</v>
       </c>
       <c r="F104" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-霉变饲料</v>
       </c>
       <c r="G104">
         <v>155</v>
@@ -5616,7 +5616,7 @@
         <v>4519</v>
       </c>
       <c r="F105" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G105">
         <v>113</v>
@@ -5666,7 +5666,7 @@
         <v>4766</v>
       </c>
       <c r="F106" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G106">
         <v>150</v>
@@ -5716,7 +5716,7 @@
         <v>5292</v>
       </c>
       <c r="F107" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G107">
         <v>144</v>
@@ -5766,7 +5766,7 @@
         <v>7498</v>
       </c>
       <c r="F108" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G108">
         <v>90</v>
@@ -5816,7 +5816,7 @@
         <v>6160</v>
       </c>
       <c r="F109" t="str">
-        <v>水质异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G109">
         <v>105</v>
@@ -5866,7 +5866,7 @@
         <v>6306</v>
       </c>
       <c r="F110" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G110">
         <v>142</v>
@@ -5916,7 +5916,7 @@
         <v>6416</v>
       </c>
       <c r="F111" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G111">
         <v>134</v>
@@ -5966,7 +5966,7 @@
         <v>6881</v>
       </c>
       <c r="F112" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G112">
         <v>104</v>
@@ -6016,7 +6016,7 @@
         <v>5837</v>
       </c>
       <c r="F113" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G113">
         <v>94</v>
@@ -6066,7 +6066,7 @@
         <v>5434</v>
       </c>
       <c r="F114" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-霉变饲料</v>
       </c>
       <c r="G114">
         <v>136</v>
@@ -6116,7 +6116,7 @@
         <v>3056</v>
       </c>
       <c r="F115" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G115">
         <v>177</v>
@@ -6166,7 +6166,7 @@
         <v>7228</v>
       </c>
       <c r="F116" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G116">
         <v>103</v>
@@ -6216,7 +6216,7 @@
         <v>6499</v>
       </c>
       <c r="F117" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G117">
         <v>141</v>
@@ -6266,7 +6266,7 @@
         <v>4225</v>
       </c>
       <c r="F118" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G118">
         <v>147</v>
@@ -6316,7 +6316,7 @@
         <v>6896</v>
       </c>
       <c r="F119" t="str">
-        <v>疾病</v>
+        <v>疾病-水霉病</v>
       </c>
       <c r="G119">
         <v>143</v>
@@ -6366,7 +6366,7 @@
         <v>5408</v>
       </c>
       <c r="F120" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G120">
         <v>146</v>
@@ -6416,7 +6416,7 @@
         <v>6822</v>
       </c>
       <c r="F121" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G121">
         <v>163</v>
@@ -6466,7 +6466,7 @@
         <v>7263</v>
       </c>
       <c r="F122" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G122">
         <v>129</v>
@@ -6516,7 +6516,7 @@
         <v>3526</v>
       </c>
       <c r="F123" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G123">
         <v>180</v>
@@ -6566,7 +6566,7 @@
         <v>3145</v>
       </c>
       <c r="F124" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G124">
         <v>91</v>
@@ -6616,7 +6616,7 @@
         <v>6388</v>
       </c>
       <c r="F125" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G125">
         <v>113</v>
@@ -6666,7 +6666,7 @@
         <v>3932</v>
       </c>
       <c r="F126" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G126">
         <v>147</v>
@@ -6716,7 +6716,7 @@
         <v>3187</v>
       </c>
       <c r="F127" t="str">
-        <v>疾病</v>
+        <v>疾病-肠炎病</v>
       </c>
       <c r="G127">
         <v>121</v>
@@ -6766,7 +6766,7 @@
         <v>7745</v>
       </c>
       <c r="F128" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G128">
         <v>152</v>
@@ -6816,7 +6816,7 @@
         <v>4037</v>
       </c>
       <c r="F129" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G129">
         <v>94</v>
@@ -6866,7 +6866,7 @@
         <v>5911</v>
       </c>
       <c r="F130" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G130">
         <v>178</v>
@@ -6916,7 +6916,7 @@
         <v>4986</v>
       </c>
       <c r="F131" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G131">
         <v>99</v>
@@ -6966,7 +6966,7 @@
         <v>3147</v>
       </c>
       <c r="F132" t="str">
-        <v>疾病</v>
+        <v>疾病-指环虫感染</v>
       </c>
       <c r="G132">
         <v>102</v>
@@ -7016,7 +7016,7 @@
         <v>6902</v>
       </c>
       <c r="F133" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G133">
         <v>107</v>
@@ -7066,7 +7066,7 @@
         <v>5493</v>
       </c>
       <c r="F134" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G134">
         <v>137</v>
@@ -7116,7 +7116,7 @@
         <v>5718</v>
       </c>
       <c r="F135" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G135">
         <v>142</v>
@@ -7166,7 +7166,7 @@
         <v>5183</v>
       </c>
       <c r="F136" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G136">
         <v>133</v>
@@ -7216,7 +7216,7 @@
         <v>5346</v>
       </c>
       <c r="F137" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G137">
         <v>92</v>
@@ -7266,7 +7266,7 @@
         <v>3729</v>
       </c>
       <c r="F138" t="str">
-        <v>疾病</v>
+        <v>疾病-车轮虫感染</v>
       </c>
       <c r="G138">
         <v>169</v>
@@ -7316,7 +7316,7 @@
         <v>4675</v>
       </c>
       <c r="F139" t="str">
-        <v>水质异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G139">
         <v>145</v>
@@ -7366,7 +7366,7 @@
         <v>6812</v>
       </c>
       <c r="F140" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G140">
         <v>115</v>
@@ -7416,7 +7416,7 @@
         <v>6590</v>
       </c>
       <c r="F141" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G141">
         <v>154</v>
@@ -7466,7 +7466,7 @@
         <v>3627</v>
       </c>
       <c r="F142" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G142">
         <v>128</v>
@@ -7516,7 +7516,7 @@
         <v>3521</v>
       </c>
       <c r="F143" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G143">
         <v>132</v>
@@ -7566,7 +7566,7 @@
         <v>3456</v>
       </c>
       <c r="F144" t="str">
-        <v>疾病</v>
+        <v>疾病-指环虫感染</v>
       </c>
       <c r="G144">
         <v>174</v>
@@ -7616,7 +7616,7 @@
         <v>6920</v>
       </c>
       <c r="F145" t="str">
-        <v>疾病</v>
+        <v>疾病-水霉病</v>
       </c>
       <c r="G145">
         <v>158</v>
@@ -7666,7 +7666,7 @@
         <v>5810</v>
       </c>
       <c r="F146" t="str">
-        <v>疾病</v>
+        <v>疾病-车轮虫感染</v>
       </c>
       <c r="G146">
         <v>114</v>
@@ -7716,7 +7716,7 @@
         <v>5623</v>
       </c>
       <c r="F147" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G147">
         <v>167</v>
@@ -7766,7 +7766,7 @@
         <v>4931</v>
       </c>
       <c r="F148" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G148">
         <v>106</v>
@@ -7816,7 +7816,7 @@
         <v>6998</v>
       </c>
       <c r="F149" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G149">
         <v>162</v>
@@ -7866,7 +7866,7 @@
         <v>5770</v>
       </c>
       <c r="F150" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G150">
         <v>163</v>
@@ -7916,7 +7916,7 @@
         <v>5857</v>
       </c>
       <c r="F151" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G151">
         <v>96</v>
@@ -7966,7 +7966,7 @@
         <v>7135</v>
       </c>
       <c r="F152" t="str">
-        <v>疾病</v>
+        <v>疾病-指环虫感染</v>
       </c>
       <c r="G152">
         <v>145</v>
@@ -8016,7 +8016,7 @@
         <v>6342</v>
       </c>
       <c r="F153" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G153">
         <v>157</v>
@@ -8066,7 +8066,7 @@
         <v>4016</v>
       </c>
       <c r="F154" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G154">
         <v>117</v>
@@ -8116,7 +8116,7 @@
         <v>3849</v>
       </c>
       <c r="F155" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G155">
         <v>102</v>
@@ -8166,7 +8166,7 @@
         <v>3565</v>
       </c>
       <c r="F156" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G156">
         <v>140</v>
@@ -8216,7 +8216,7 @@
         <v>6202</v>
       </c>
       <c r="F157" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G157">
         <v>155</v>
@@ -8266,7 +8266,7 @@
         <v>5836</v>
       </c>
       <c r="F158" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G158">
         <v>107</v>
@@ -8316,7 +8316,7 @@
         <v>3443</v>
       </c>
       <c r="F159" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G159">
         <v>157</v>
@@ -8366,7 +8366,7 @@
         <v>5110</v>
       </c>
       <c r="F160" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G160">
         <v>142</v>
@@ -8416,7 +8416,7 @@
         <v>7161</v>
       </c>
       <c r="F161" t="str">
-        <v>水质异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G161">
         <v>129</v>
@@ -8466,7 +8466,7 @@
         <v>5368</v>
       </c>
       <c r="F162" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G162">
         <v>131</v>
@@ -8516,7 +8516,7 @@
         <v>6875</v>
       </c>
       <c r="F163" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G163">
         <v>109</v>
@@ -8566,7 +8566,7 @@
         <v>3862</v>
       </c>
       <c r="F164" t="str">
-        <v>疾病</v>
+        <v>疾病-肠炎病</v>
       </c>
       <c r="G164">
         <v>136</v>
@@ -8616,7 +8616,7 @@
         <v>3203</v>
       </c>
       <c r="F165" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G165">
         <v>117</v>
@@ -8666,7 +8666,7 @@
         <v>7389</v>
       </c>
       <c r="F166" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G166">
         <v>127</v>
@@ -8716,7 +8716,7 @@
         <v>3412</v>
       </c>
       <c r="F167" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-霉变饲料</v>
       </c>
       <c r="G167">
         <v>166</v>
@@ -8766,7 +8766,7 @@
         <v>6626</v>
       </c>
       <c r="F168" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G168">
         <v>150</v>
@@ -8816,7 +8816,7 @@
         <v>4302</v>
       </c>
       <c r="F169" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G169">
         <v>162</v>
@@ -8866,7 +8866,7 @@
         <v>4049</v>
       </c>
       <c r="F170" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G170">
         <v>103</v>
@@ -8916,7 +8916,7 @@
         <v>4236</v>
       </c>
       <c r="F171" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G171">
         <v>136</v>
@@ -8966,7 +8966,7 @@
         <v>3648</v>
       </c>
       <c r="F172" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G172">
         <v>107</v>
@@ -9016,7 +9016,7 @@
         <v>4958</v>
       </c>
       <c r="F173" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G173">
         <v>104</v>
@@ -9066,7 +9066,7 @@
         <v>7029</v>
       </c>
       <c r="F174" t="str">
-        <v>疾病</v>
+        <v>疾病-肠炎病</v>
       </c>
       <c r="G174">
         <v>117</v>
@@ -9116,7 +9116,7 @@
         <v>7047</v>
       </c>
       <c r="F175" t="str">
-        <v>疾病</v>
+        <v>疾病-细菌性烂鳃病</v>
       </c>
       <c r="G175">
         <v>175</v>
@@ -9166,7 +9166,7 @@
         <v>6920</v>
       </c>
       <c r="F176" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G176">
         <v>123</v>
@@ -9216,7 +9216,7 @@
         <v>4704</v>
       </c>
       <c r="F177" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G177">
         <v>172</v>
@@ -9266,7 +9266,7 @@
         <v>5095</v>
       </c>
       <c r="F178" t="str">
-        <v>疾病</v>
+        <v>疾病-指环虫感染</v>
       </c>
       <c r="G178">
         <v>169</v>
@@ -9316,7 +9316,7 @@
         <v>5193</v>
       </c>
       <c r="F179" t="str">
-        <v>疾病</v>
+        <v>疾病-车轮虫感染</v>
       </c>
       <c r="G179">
         <v>94</v>
@@ -9366,7 +9366,7 @@
         <v>7130</v>
       </c>
       <c r="F180" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G180">
         <v>172</v>
@@ -9416,7 +9416,7 @@
         <v>4071</v>
       </c>
       <c r="F181" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G181">
         <v>178</v>
@@ -9466,7 +9466,7 @@
         <v>6686</v>
       </c>
       <c r="F182" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-霉变饲料</v>
       </c>
       <c r="G182">
         <v>119</v>
@@ -9516,7 +9516,7 @@
         <v>3017</v>
       </c>
       <c r="F183" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G183">
         <v>170</v>
@@ -9566,7 +9566,7 @@
         <v>7450</v>
       </c>
       <c r="F184" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G184">
         <v>113</v>
@@ -9616,7 +9616,7 @@
         <v>6836</v>
       </c>
       <c r="F185" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G185">
         <v>98</v>
@@ -9666,7 +9666,7 @@
         <v>6132</v>
       </c>
       <c r="F186" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G186">
         <v>143</v>
@@ -9716,7 +9716,7 @@
         <v>7055</v>
       </c>
       <c r="F187" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G187">
         <v>94</v>
@@ -9766,7 +9766,7 @@
         <v>5913</v>
       </c>
       <c r="F188" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-霉变饲料</v>
       </c>
       <c r="G188">
         <v>154</v>
@@ -9816,7 +9816,7 @@
         <v>6422</v>
       </c>
       <c r="F189" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G189">
         <v>135</v>
@@ -9866,7 +9866,7 @@
         <v>3661</v>
       </c>
       <c r="F190" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G190">
         <v>107</v>
@@ -9916,7 +9916,7 @@
         <v>4525</v>
       </c>
       <c r="F191" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G191">
         <v>107</v>
@@ -9966,7 +9966,7 @@
         <v>6257</v>
       </c>
       <c r="F192" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G192">
         <v>121</v>
@@ -10016,7 +10016,7 @@
         <v>6260</v>
       </c>
       <c r="F193" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G193">
         <v>114</v>
@@ -10066,7 +10066,7 @@
         <v>4145</v>
       </c>
       <c r="F194" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G194">
         <v>144</v>
@@ -10116,7 +10116,7 @@
         <v>7539</v>
       </c>
       <c r="F195" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G195">
         <v>137</v>
@@ -10166,7 +10166,7 @@
         <v>4360</v>
       </c>
       <c r="F196" t="str">
-        <v>水质异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G196">
         <v>166</v>
@@ -10216,7 +10216,7 @@
         <v>3904</v>
       </c>
       <c r="F197" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G197">
         <v>114</v>
@@ -10266,7 +10266,7 @@
         <v>7428</v>
       </c>
       <c r="F198" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G198">
         <v>161</v>
@@ -10316,7 +10316,7 @@
         <v>6647</v>
       </c>
       <c r="F199" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G199">
         <v>106</v>
@@ -10366,7 +10366,7 @@
         <v>3483</v>
       </c>
       <c r="F200" t="str">
-        <v>疾病</v>
+        <v>疾病-指环虫感染</v>
       </c>
       <c r="G200">
         <v>101</v>
@@ -10416,7 +10416,7 @@
         <v>5068</v>
       </c>
       <c r="F201" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G201">
         <v>162</v>
@@ -10466,7 +10466,7 @@
         <v>7609</v>
       </c>
       <c r="F202" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G202">
         <v>90</v>
@@ -10516,7 +10516,7 @@
         <v>6773</v>
       </c>
       <c r="F203" t="str">
-        <v>疾病</v>
+        <v>疾病-指环虫感染</v>
       </c>
       <c r="G203">
         <v>126</v>
@@ -10566,7 +10566,7 @@
         <v>3164</v>
       </c>
       <c r="F204" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G204">
         <v>162</v>
@@ -10616,7 +10616,7 @@
         <v>3669</v>
       </c>
       <c r="F205" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G205">
         <v>108</v>
@@ -10666,7 +10666,7 @@
         <v>6537</v>
       </c>
       <c r="F206" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G206">
         <v>164</v>
@@ -10716,7 +10716,7 @@
         <v>6121</v>
       </c>
       <c r="F207" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G207">
         <v>160</v>
@@ -10766,7 +10766,7 @@
         <v>5048</v>
       </c>
       <c r="F208" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G208">
         <v>140</v>
@@ -10816,7 +10816,7 @@
         <v>6811</v>
       </c>
       <c r="F209" t="str">
-        <v>水质异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G209">
         <v>139</v>
@@ -10866,7 +10866,7 @@
         <v>7147</v>
       </c>
       <c r="F210" t="str">
-        <v>疾病</v>
+        <v>疾病-车轮虫感染</v>
       </c>
       <c r="G210">
         <v>105</v>
@@ -10916,7 +10916,7 @@
         <v>6453</v>
       </c>
       <c r="F211" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G211">
         <v>121</v>
@@ -10966,7 +10966,7 @@
         <v>3422</v>
       </c>
       <c r="F212" t="str">
-        <v>水质异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G212">
         <v>108</v>
@@ -11016,7 +11016,7 @@
         <v>4338</v>
       </c>
       <c r="F213" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G213">
         <v>117</v>
@@ -11066,7 +11066,7 @@
         <v>4569</v>
       </c>
       <c r="F214" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G214">
         <v>149</v>
@@ -11116,7 +11116,7 @@
         <v>3849</v>
       </c>
       <c r="F215" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G215">
         <v>122</v>
@@ -11166,7 +11166,7 @@
         <v>7374</v>
       </c>
       <c r="F216" t="str">
-        <v>疾病</v>
+        <v>疾病-指环虫感染</v>
       </c>
       <c r="G216">
         <v>133</v>
@@ -11216,7 +11216,7 @@
         <v>7112</v>
       </c>
       <c r="F217" t="str">
-        <v>疾病</v>
+        <v>疾病-水霉病</v>
       </c>
       <c r="G217">
         <v>148</v>
@@ -11266,7 +11266,7 @@
         <v>6068</v>
       </c>
       <c r="F218" t="str">
-        <v>疾病</v>
+        <v>疾病-细菌性烂鳃病</v>
       </c>
       <c r="G218">
         <v>119</v>
@@ -11316,7 +11316,7 @@
         <v>5367</v>
       </c>
       <c r="F219" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G219">
         <v>127</v>
@@ -11366,7 +11366,7 @@
         <v>6321</v>
       </c>
       <c r="F220" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G220">
         <v>134</v>
@@ -11416,7 +11416,7 @@
         <v>5072</v>
       </c>
       <c r="F221" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G221">
         <v>168</v>
@@ -11466,7 +11466,7 @@
         <v>5031</v>
       </c>
       <c r="F222" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G222">
         <v>110</v>
@@ -11516,7 +11516,7 @@
         <v>7331</v>
       </c>
       <c r="F223" t="str">
-        <v>水质异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G223">
         <v>168</v>
@@ -11566,7 +11566,7 @@
         <v>7116</v>
       </c>
       <c r="F224" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G224">
         <v>91</v>
@@ -11616,7 +11616,7 @@
         <v>3519</v>
       </c>
       <c r="F225" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G225">
         <v>105</v>
@@ -11666,7 +11666,7 @@
         <v>6606</v>
       </c>
       <c r="F226" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G226">
         <v>140</v>
@@ -11716,7 +11716,7 @@
         <v>6043</v>
       </c>
       <c r="F227" t="str">
-        <v>疾病</v>
+        <v>疾病-细菌性烂鳃病</v>
       </c>
       <c r="G227">
         <v>153</v>
@@ -11766,7 +11766,7 @@
         <v>2868</v>
       </c>
       <c r="F228" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G228">
         <v>114</v>
@@ -11816,7 +11816,7 @@
         <v>4279</v>
       </c>
       <c r="F229" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G229">
         <v>175</v>
@@ -11866,7 +11866,7 @@
         <v>5442</v>
       </c>
       <c r="F230" t="str">
-        <v>疾病</v>
+        <v>疾病-车轮虫感染</v>
       </c>
       <c r="G230">
         <v>110</v>
@@ -11916,7 +11916,7 @@
         <v>3917</v>
       </c>
       <c r="F231" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G231">
         <v>98</v>
@@ -11966,7 +11966,7 @@
         <v>3220</v>
       </c>
       <c r="F232" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G232">
         <v>153</v>
@@ -12016,7 +12016,7 @@
         <v>4120</v>
       </c>
       <c r="F233" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G233">
         <v>113</v>
@@ -12066,7 +12066,7 @@
         <v>6184</v>
       </c>
       <c r="F234" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G234">
         <v>127</v>
@@ -12116,7 +12116,7 @@
         <v>3510</v>
       </c>
       <c r="F235" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G235">
         <v>102</v>
@@ -12166,7 +12166,7 @@
         <v>6691</v>
       </c>
       <c r="F236" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G236">
         <v>129</v>
@@ -12216,7 +12216,7 @@
         <v>5016</v>
       </c>
       <c r="F237" t="str">
-        <v>疾病</v>
+        <v>疾病-指环虫感染</v>
       </c>
       <c r="G237">
         <v>168</v>
@@ -12266,7 +12266,7 @@
         <v>5830</v>
       </c>
       <c r="F238" t="str">
-        <v>水质异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G238">
         <v>120</v>
@@ -12316,7 +12316,7 @@
         <v>4996</v>
       </c>
       <c r="F239" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G239">
         <v>104</v>
@@ -12366,7 +12366,7 @@
         <v>5341</v>
       </c>
       <c r="F240" t="str">
-        <v>疾病</v>
+        <v>疾病-细菌性烂鳃病</v>
       </c>
       <c r="G240">
         <v>164</v>
@@ -12416,7 +12416,7 @@
         <v>6118</v>
       </c>
       <c r="F241" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-霉变饲料</v>
       </c>
       <c r="G241">
         <v>149</v>
@@ -12466,7 +12466,7 @@
         <v>2856</v>
       </c>
       <c r="F242" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G242">
         <v>157</v>
@@ -12516,7 +12516,7 @@
         <v>5468</v>
       </c>
       <c r="F243" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G243">
         <v>117</v>
@@ -12566,7 +12566,7 @@
         <v>3330</v>
       </c>
       <c r="F244" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G244">
         <v>114</v>
@@ -12616,7 +12616,7 @@
         <v>3024</v>
       </c>
       <c r="F245" t="str">
-        <v>疾病</v>
+        <v>疾病-指环虫感染</v>
       </c>
       <c r="G245">
         <v>135</v>
@@ -12666,7 +12666,7 @@
         <v>5227</v>
       </c>
       <c r="F246" t="str">
-        <v>疾病</v>
+        <v>疾病-细菌性烂鳃病</v>
       </c>
       <c r="G246">
         <v>165</v>
@@ -12716,7 +12716,7 @@
         <v>6998</v>
       </c>
       <c r="F247" t="str">
-        <v>疾病</v>
+        <v>疾病-细菌性烂鳃病</v>
       </c>
       <c r="G247">
         <v>169</v>
@@ -12766,7 +12766,7 @@
         <v>4931</v>
       </c>
       <c r="F248" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G248">
         <v>127</v>
@@ -12816,7 +12816,7 @@
         <v>3187</v>
       </c>
       <c r="F249" t="str">
-        <v>疾病</v>
+        <v>疾病-肠炎病</v>
       </c>
       <c r="G249">
         <v>90</v>
@@ -12866,7 +12866,7 @@
         <v>6389</v>
       </c>
       <c r="F250" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G250">
         <v>159</v>
@@ -12916,7 +12916,7 @@
         <v>4081</v>
       </c>
       <c r="F251" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G251">
         <v>128</v>
@@ -12966,7 +12966,7 @@
         <v>4079</v>
       </c>
       <c r="F252" t="str">
-        <v>疾病</v>
+        <v>疾病-细菌性烂鳃病</v>
       </c>
       <c r="G252">
         <v>168</v>
@@ -13016,7 +13016,7 @@
         <v>4974</v>
       </c>
       <c r="F253" t="str">
-        <v>疾病</v>
+        <v>疾病-指环虫感染</v>
       </c>
       <c r="G253">
         <v>163</v>
@@ -13066,7 +13066,7 @@
         <v>7429</v>
       </c>
       <c r="F254" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G254">
         <v>134</v>
@@ -13116,7 +13116,7 @@
         <v>2967</v>
       </c>
       <c r="F255" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G255">
         <v>145</v>
@@ -13166,7 +13166,7 @@
         <v>5459</v>
       </c>
       <c r="F256" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G256">
         <v>133</v>
@@ -13216,7 +13216,7 @@
         <v>7742</v>
       </c>
       <c r="F257" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G257">
         <v>166</v>
@@ -13266,7 +13266,7 @@
         <v>6993</v>
       </c>
       <c r="F258" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G258">
         <v>166</v>
@@ -13316,7 +13316,7 @@
         <v>4076</v>
       </c>
       <c r="F259" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G259">
         <v>177</v>
@@ -13366,7 +13366,7 @@
         <v>6998</v>
       </c>
       <c r="F260" t="str">
-        <v>疾病</v>
+        <v>疾病-指环虫感染</v>
       </c>
       <c r="G260">
         <v>135</v>
@@ -13416,7 +13416,7 @@
         <v>4266</v>
       </c>
       <c r="F261" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G261">
         <v>163</v>
@@ -13466,7 +13466,7 @@
         <v>4142</v>
       </c>
       <c r="F262" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G262">
         <v>166</v>
@@ -13516,7 +13516,7 @@
         <v>3441</v>
       </c>
       <c r="F263" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G263">
         <v>152</v>
@@ -13566,7 +13566,7 @@
         <v>4486</v>
       </c>
       <c r="F264" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-霉变饲料</v>
       </c>
       <c r="G264">
         <v>155</v>
@@ -13616,7 +13616,7 @@
         <v>3703</v>
       </c>
       <c r="F265" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-霉变饲料</v>
       </c>
       <c r="G265">
         <v>128</v>
@@ -13666,7 +13666,7 @@
         <v>2947</v>
       </c>
       <c r="F266" t="str">
-        <v>疾病</v>
+        <v>疾病-车轮虫感染</v>
       </c>
       <c r="G266">
         <v>91</v>
@@ -13716,7 +13716,7 @@
         <v>4346</v>
       </c>
       <c r="F267" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G267">
         <v>107</v>
@@ -13766,7 +13766,7 @@
         <v>3095</v>
       </c>
       <c r="F268" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-霉变饲料</v>
       </c>
       <c r="G268">
         <v>144</v>
@@ -13816,7 +13816,7 @@
         <v>6109</v>
       </c>
       <c r="F269" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G269">
         <v>98</v>
@@ -13866,7 +13866,7 @@
         <v>4791</v>
       </c>
       <c r="F270" t="str">
-        <v>疾病</v>
+        <v>疾病-肠炎病</v>
       </c>
       <c r="G270">
         <v>97</v>
@@ -13916,7 +13916,7 @@
         <v>5825</v>
       </c>
       <c r="F271" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G271">
         <v>94</v>
@@ -13966,7 +13966,7 @@
         <v>4660</v>
       </c>
       <c r="F272" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G272">
         <v>163</v>
@@ -14016,7 +14016,7 @@
         <v>7404</v>
       </c>
       <c r="F273" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-霉变饲料</v>
       </c>
       <c r="G273">
         <v>90</v>
@@ -14066,7 +14066,7 @@
         <v>3426</v>
       </c>
       <c r="F274" t="str">
-        <v>水质异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G274">
         <v>129</v>
@@ -14116,7 +14116,7 @@
         <v>6399</v>
       </c>
       <c r="F275" t="str">
-        <v>疾病</v>
+        <v>疾病-肠炎病</v>
       </c>
       <c r="G275">
         <v>157</v>
@@ -14166,7 +14166,7 @@
         <v>3174</v>
       </c>
       <c r="F276" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G276">
         <v>130</v>
@@ -14216,7 +14216,7 @@
         <v>4099</v>
       </c>
       <c r="F277" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G277">
         <v>145</v>
@@ -14266,7 +14266,7 @@
         <v>3410</v>
       </c>
       <c r="F278" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G278">
         <v>144</v>
@@ -14316,7 +14316,7 @@
         <v>7049</v>
       </c>
       <c r="F279" t="str">
-        <v>疾病</v>
+        <v>疾病-肠炎病</v>
       </c>
       <c r="G279">
         <v>114</v>
@@ -14366,7 +14366,7 @@
         <v>7336</v>
       </c>
       <c r="F280" t="str">
-        <v>水质异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G280">
         <v>110</v>
@@ -14416,7 +14416,7 @@
         <v>5759</v>
       </c>
       <c r="F281" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G281">
         <v>161</v>
@@ -14466,7 +14466,7 @@
         <v>6295</v>
       </c>
       <c r="F282" t="str">
-        <v>疾病</v>
+        <v>疾病-肠炎病</v>
       </c>
       <c r="G282">
         <v>167</v>
@@ -14516,7 +14516,7 @@
         <v>5865</v>
       </c>
       <c r="F283" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G283">
         <v>170</v>
@@ -14566,7 +14566,7 @@
         <v>4328</v>
       </c>
       <c r="F284" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G284">
         <v>159</v>
@@ -14616,7 +14616,7 @@
         <v>6107</v>
       </c>
       <c r="F285" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G285">
         <v>148</v>
@@ -14666,7 +14666,7 @@
         <v>7422</v>
       </c>
       <c r="F286" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G286">
         <v>96</v>
@@ -14716,7 +14716,7 @@
         <v>4071</v>
       </c>
       <c r="F287" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G287">
         <v>117</v>
@@ -14766,7 +14766,7 @@
         <v>6240</v>
       </c>
       <c r="F288" t="str">
-        <v>水质异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G288">
         <v>104</v>
@@ -14816,7 +14816,7 @@
         <v>4914</v>
       </c>
       <c r="F289" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-霉变饲料</v>
       </c>
       <c r="G289">
         <v>118</v>
@@ -14866,7 +14866,7 @@
         <v>6334</v>
       </c>
       <c r="F290" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-霉变饲料</v>
       </c>
       <c r="G290">
         <v>119</v>
@@ -14916,7 +14916,7 @@
         <v>6656</v>
       </c>
       <c r="F291" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G291">
         <v>171</v>
@@ -14966,7 +14966,7 @@
         <v>3024</v>
       </c>
       <c r="F292" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G292">
         <v>109</v>
@@ -15016,7 +15016,7 @@
         <v>3239</v>
       </c>
       <c r="F293" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G293">
         <v>173</v>
@@ -15066,7 +15066,7 @@
         <v>7792</v>
       </c>
       <c r="F294" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G294">
         <v>151</v>
@@ -15116,7 +15116,7 @@
         <v>4650</v>
       </c>
       <c r="F295" t="str">
-        <v>疾病</v>
+        <v>疾病-肠炎病</v>
       </c>
       <c r="G295">
         <v>117</v>
@@ -15166,7 +15166,7 @@
         <v>4328</v>
       </c>
       <c r="F296" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G296">
         <v>161</v>
@@ -15216,7 +15216,7 @@
         <v>6105</v>
       </c>
       <c r="F297" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G297">
         <v>156</v>
@@ -15266,7 +15266,7 @@
         <v>4193</v>
       </c>
       <c r="F298" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G298">
         <v>171</v>
@@ -15316,7 +15316,7 @@
         <v>7510</v>
       </c>
       <c r="F299" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G299">
         <v>132</v>
@@ -15366,7 +15366,7 @@
         <v>3609</v>
       </c>
       <c r="F300" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G300">
         <v>90</v>
@@ -15416,7 +15416,7 @@
         <v>4268</v>
       </c>
       <c r="F301" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G301">
         <v>168</v>
@@ -15466,7 +15466,7 @@
         <v>3366</v>
       </c>
       <c r="F302" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G302">
         <v>123</v>
@@ -15516,7 +15516,7 @@
         <v>5113</v>
       </c>
       <c r="F303" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G303">
         <v>134</v>
@@ -15566,7 +15566,7 @@
         <v>6499</v>
       </c>
       <c r="F304" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G304">
         <v>109</v>
@@ -15616,7 +15616,7 @@
         <v>5863</v>
       </c>
       <c r="F305" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G305">
         <v>104</v>
@@ -15666,7 +15666,7 @@
         <v>7209</v>
       </c>
       <c r="F306" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G306">
         <v>104</v>
@@ -15716,7 +15716,7 @@
         <v>7745</v>
       </c>
       <c r="F307" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G307">
         <v>143</v>
@@ -15766,7 +15766,7 @@
         <v>7749</v>
       </c>
       <c r="F308" t="str">
-        <v>疾病</v>
+        <v>疾病-肠炎病</v>
       </c>
       <c r="G308">
         <v>131</v>
@@ -15816,7 +15816,7 @@
         <v>4464</v>
       </c>
       <c r="F309" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G309">
         <v>149</v>
@@ -15866,7 +15866,7 @@
         <v>2906</v>
       </c>
       <c r="F310" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-霉变饲料</v>
       </c>
       <c r="G310">
         <v>158</v>
@@ -15916,7 +15916,7 @@
         <v>4423</v>
       </c>
       <c r="F311" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G311">
         <v>94</v>
@@ -15966,7 +15966,7 @@
         <v>7669</v>
       </c>
       <c r="F312" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G312">
         <v>141</v>
@@ -16016,7 +16016,7 @@
         <v>4810</v>
       </c>
       <c r="F313" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G313">
         <v>145</v>
@@ -16066,7 +16066,7 @@
         <v>5495</v>
       </c>
       <c r="F314" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G314">
         <v>128</v>
@@ -16116,7 +16116,7 @@
         <v>3869</v>
       </c>
       <c r="F315" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G315">
         <v>166</v>
@@ -16166,7 +16166,7 @@
         <v>2968</v>
       </c>
       <c r="F316" t="str">
-        <v>疾病</v>
+        <v>疾病-肠炎病</v>
       </c>
       <c r="G316">
         <v>94</v>
@@ -16216,7 +16216,7 @@
         <v>4503</v>
       </c>
       <c r="F317" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G317">
         <v>146</v>
@@ -16266,7 +16266,7 @@
         <v>4943</v>
       </c>
       <c r="F318" t="str">
-        <v>疾病</v>
+        <v>疾病-细菌性烂鳃病</v>
       </c>
       <c r="G318">
         <v>102</v>
@@ -16316,7 +16316,7 @@
         <v>4213</v>
       </c>
       <c r="F319" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G319">
         <v>108</v>
@@ -16366,7 +16366,7 @@
         <v>4478</v>
       </c>
       <c r="F320" t="str">
-        <v>水质异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G320">
         <v>116</v>
@@ -16416,7 +16416,7 @@
         <v>7587</v>
       </c>
       <c r="F321" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G321">
         <v>160</v>
@@ -16466,7 +16466,7 @@
         <v>4446</v>
       </c>
       <c r="F322" t="str">
-        <v>疾病</v>
+        <v>疾病-细菌性烂鳃病</v>
       </c>
       <c r="G322">
         <v>174</v>
@@ -16516,7 +16516,7 @@
         <v>3408</v>
       </c>
       <c r="F323" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G323">
         <v>154</v>
@@ -16566,7 +16566,7 @@
         <v>3573</v>
       </c>
       <c r="F324" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-霉变饲料</v>
       </c>
       <c r="G324">
         <v>108</v>
@@ -16616,7 +16616,7 @@
         <v>5674</v>
       </c>
       <c r="F325" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G325">
         <v>140</v>
@@ -16666,7 +16666,7 @@
         <v>7529</v>
       </c>
       <c r="F326" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G326">
         <v>177</v>
@@ -16716,7 +16716,7 @@
         <v>6701</v>
       </c>
       <c r="F327" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G327">
         <v>119</v>
@@ -16766,7 +16766,7 @@
         <v>4970</v>
       </c>
       <c r="F328" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G328">
         <v>161</v>
@@ -16816,7 +16816,7 @@
         <v>6182</v>
       </c>
       <c r="F329" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G329">
         <v>145</v>
@@ -16866,7 +16866,7 @@
         <v>7710</v>
       </c>
       <c r="F330" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G330">
         <v>135</v>
@@ -16916,7 +16916,7 @@
         <v>5804</v>
       </c>
       <c r="F331" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G331">
         <v>120</v>
@@ -16966,7 +16966,7 @@
         <v>5962</v>
       </c>
       <c r="F332" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G332">
         <v>143</v>
@@ -17016,7 +17016,7 @@
         <v>5792</v>
       </c>
       <c r="F333" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G333">
         <v>163</v>
@@ -17066,7 +17066,7 @@
         <v>4846</v>
       </c>
       <c r="F334" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G334">
         <v>148</v>
@@ -17116,7 +17116,7 @@
         <v>6583</v>
       </c>
       <c r="F335" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G335">
         <v>136</v>
@@ -17166,7 +17166,7 @@
         <v>5762</v>
       </c>
       <c r="F336" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G336">
         <v>173</v>
@@ -17216,7 +17216,7 @@
         <v>5213</v>
       </c>
       <c r="F337" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G337">
         <v>142</v>
@@ -17266,7 +17266,7 @@
         <v>3295</v>
       </c>
       <c r="F338" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G338">
         <v>145</v>
@@ -17316,7 +17316,7 @@
         <v>3742</v>
       </c>
       <c r="F339" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G339">
         <v>177</v>
@@ -17366,7 +17366,7 @@
         <v>5221</v>
       </c>
       <c r="F340" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G340">
         <v>143</v>
@@ -17416,7 +17416,7 @@
         <v>6799</v>
       </c>
       <c r="F341" t="str">
-        <v>疾病</v>
+        <v>疾病-指环虫感染</v>
       </c>
       <c r="G341">
         <v>171</v>
@@ -17466,7 +17466,7 @@
         <v>4757</v>
       </c>
       <c r="F342" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G342">
         <v>115</v>
@@ -17516,7 +17516,7 @@
         <v>6015</v>
       </c>
       <c r="F343" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G343">
         <v>92</v>
@@ -17566,7 +17566,7 @@
         <v>3839</v>
       </c>
       <c r="F344" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G344">
         <v>92</v>
@@ -17616,7 +17616,7 @@
         <v>7146</v>
       </c>
       <c r="F345" t="str">
-        <v>水质异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G345">
         <v>91</v>
@@ -17666,7 +17666,7 @@
         <v>4163</v>
       </c>
       <c r="F346" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G346">
         <v>157</v>
@@ -17716,7 +17716,7 @@
         <v>6626</v>
       </c>
       <c r="F347" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G347">
         <v>110</v>
@@ -17766,7 +17766,7 @@
         <v>5696</v>
       </c>
       <c r="F348" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G348">
         <v>115</v>
@@ -17816,7 +17816,7 @@
         <v>6598</v>
       </c>
       <c r="F349" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G349">
         <v>125</v>
@@ -17866,7 +17866,7 @@
         <v>3129</v>
       </c>
       <c r="F350" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G350">
         <v>150</v>
@@ -17916,7 +17916,7 @@
         <v>6818</v>
       </c>
       <c r="F351" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G351">
         <v>168</v>
@@ -17966,7 +17966,7 @@
         <v>6078</v>
       </c>
       <c r="F352" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G352">
         <v>177</v>
@@ -18016,7 +18016,7 @@
         <v>4629</v>
       </c>
       <c r="F353" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G353">
         <v>157</v>
@@ -18066,7 +18066,7 @@
         <v>6559</v>
       </c>
       <c r="F354" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G354">
         <v>165</v>
@@ -18116,7 +18116,7 @@
         <v>6274</v>
       </c>
       <c r="F355" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G355">
         <v>120</v>
@@ -18166,7 +18166,7 @@
         <v>3537</v>
       </c>
       <c r="F356" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G356">
         <v>121</v>
@@ -18216,7 +18216,7 @@
         <v>4791</v>
       </c>
       <c r="F357" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G357">
         <v>122</v>
@@ -18266,7 +18266,7 @@
         <v>5250</v>
       </c>
       <c r="F358" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G358">
         <v>141</v>
@@ -18316,7 +18316,7 @@
         <v>5493</v>
       </c>
       <c r="F359" t="str">
-        <v>疾病</v>
+        <v>疾病-车轮虫感染</v>
       </c>
       <c r="G359">
         <v>179</v>
@@ -18366,7 +18366,7 @@
         <v>3350</v>
       </c>
       <c r="F360" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G360">
         <v>160</v>
@@ -18416,7 +18416,7 @@
         <v>7283</v>
       </c>
       <c r="F361" t="str">
-        <v>疾病</v>
+        <v>疾病-水霉病</v>
       </c>
       <c r="G361">
         <v>167</v>
@@ -18466,7 +18466,7 @@
         <v>7413</v>
       </c>
       <c r="F362" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G362">
         <v>101</v>
@@ -18516,7 +18516,7 @@
         <v>3362</v>
       </c>
       <c r="F363" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G363">
         <v>96</v>
@@ -18566,7 +18566,7 @@
         <v>4697</v>
       </c>
       <c r="F364" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G364">
         <v>178</v>
@@ -18616,7 +18616,7 @@
         <v>6818</v>
       </c>
       <c r="F365" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G365">
         <v>113</v>
@@ -18666,7 +18666,7 @@
         <v>4385</v>
       </c>
       <c r="F366" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G366">
         <v>98</v>
@@ -18716,7 +18716,7 @@
         <v>5838</v>
       </c>
       <c r="F367" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G367">
         <v>112</v>
@@ -18766,7 +18766,7 @@
         <v>6272</v>
       </c>
       <c r="F368" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G368">
         <v>159</v>
@@ -18816,7 +18816,7 @@
         <v>7603</v>
       </c>
       <c r="F369" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G369">
         <v>95</v>
@@ -18866,7 +18866,7 @@
         <v>5775</v>
       </c>
       <c r="F370" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G370">
         <v>104</v>
@@ -18916,7 +18916,7 @@
         <v>7069</v>
       </c>
       <c r="F371" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G371">
         <v>157</v>
@@ -18966,7 +18966,7 @@
         <v>4645</v>
       </c>
       <c r="F372" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G372">
         <v>96</v>
@@ -19016,7 +19016,7 @@
         <v>3983</v>
       </c>
       <c r="F373" t="str">
-        <v>疾病</v>
+        <v>疾病-指环虫感染</v>
       </c>
       <c r="G373">
         <v>125</v>
@@ -19066,7 +19066,7 @@
         <v>4707</v>
       </c>
       <c r="F374" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G374">
         <v>110</v>
@@ -19116,7 +19116,7 @@
         <v>3988</v>
       </c>
       <c r="F375" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G375">
         <v>157</v>
@@ -19166,7 +19166,7 @@
         <v>5890</v>
       </c>
       <c r="F376" t="str">
-        <v>疾病</v>
+        <v>疾病-细菌性烂鳃病</v>
       </c>
       <c r="G376">
         <v>142</v>
@@ -19216,7 +19216,7 @@
         <v>6582</v>
       </c>
       <c r="F377" t="str">
-        <v>疾病</v>
+        <v>疾病-车轮虫感染</v>
       </c>
       <c r="G377">
         <v>171</v>
@@ -19266,7 +19266,7 @@
         <v>4332</v>
       </c>
       <c r="F378" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G378">
         <v>131</v>
@@ -19316,7 +19316,7 @@
         <v>3078</v>
       </c>
       <c r="F379" t="str">
-        <v>水质异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G379">
         <v>112</v>
@@ -19366,7 +19366,7 @@
         <v>4040</v>
       </c>
       <c r="F380" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G380">
         <v>174</v>
@@ -19416,7 +19416,7 @@
         <v>7126</v>
       </c>
       <c r="F381" t="str">
-        <v>水质异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G381">
         <v>106</v>
@@ -19466,7 +19466,7 @@
         <v>6945</v>
       </c>
       <c r="F382" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G382">
         <v>124</v>
@@ -19516,7 +19516,7 @@
         <v>4008</v>
       </c>
       <c r="F383" t="str">
-        <v>疾病</v>
+        <v>疾病-车轮虫感染</v>
       </c>
       <c r="G383">
         <v>167</v>
@@ -19566,7 +19566,7 @@
         <v>3626</v>
       </c>
       <c r="F384" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G384">
         <v>109</v>
@@ -19616,7 +19616,7 @@
         <v>5477</v>
       </c>
       <c r="F385" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G385">
         <v>162</v>
@@ -19666,7 +19666,7 @@
         <v>6522</v>
       </c>
       <c r="F386" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G386">
         <v>137</v>
@@ -19716,7 +19716,7 @@
         <v>3762</v>
       </c>
       <c r="F387" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G387">
         <v>148</v>
@@ -19766,7 +19766,7 @@
         <v>5905</v>
       </c>
       <c r="F388" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G388">
         <v>111</v>
@@ -19816,7 +19816,7 @@
         <v>3477</v>
       </c>
       <c r="F389" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G389">
         <v>100</v>
@@ -19866,7 +19866,7 @@
         <v>6853</v>
       </c>
       <c r="F390" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G390">
         <v>152</v>
@@ -19916,7 +19916,7 @@
         <v>5702</v>
       </c>
       <c r="F391" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G391">
         <v>153</v>
@@ -19966,7 +19966,7 @@
         <v>3651</v>
       </c>
       <c r="F392" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G392">
         <v>174</v>
@@ -20016,7 +20016,7 @@
         <v>3547</v>
       </c>
       <c r="F393" t="str">
-        <v>水质异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G393">
         <v>145</v>
@@ -20066,7 +20066,7 @@
         <v>6048</v>
       </c>
       <c r="F394" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G394">
         <v>172</v>
@@ -20116,7 +20116,7 @@
         <v>5702</v>
       </c>
       <c r="F395" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G395">
         <v>172</v>
@@ -20166,7 +20166,7 @@
         <v>7769</v>
       </c>
       <c r="F396" t="str">
-        <v>水质异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G396">
         <v>142</v>
@@ -20216,7 +20216,7 @@
         <v>6823</v>
       </c>
       <c r="F397" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G397">
         <v>171</v>
@@ -20266,7 +20266,7 @@
         <v>4959</v>
       </c>
       <c r="F398" t="str">
-        <v>水质异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G398">
         <v>173</v>
@@ -20316,7 +20316,7 @@
         <v>5731</v>
       </c>
       <c r="F399" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G399">
         <v>178</v>
@@ -20366,7 +20366,7 @@
         <v>3380</v>
       </c>
       <c r="F400" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-霉变饲料</v>
       </c>
       <c r="G400">
         <v>179</v>
@@ -20416,7 +20416,7 @@
         <v>6662</v>
       </c>
       <c r="F401" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G401">
         <v>149</v>
@@ -20466,7 +20466,7 @@
         <v>4188</v>
       </c>
       <c r="F402" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G402">
         <v>98</v>
@@ -20516,7 +20516,7 @@
         <v>7174</v>
       </c>
       <c r="F403" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G403">
         <v>147</v>
@@ -20566,7 +20566,7 @@
         <v>3260</v>
       </c>
       <c r="F404" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-霉变饲料</v>
       </c>
       <c r="G404">
         <v>128</v>
@@ -20616,7 +20616,7 @@
         <v>4846</v>
       </c>
       <c r="F405" t="str">
-        <v>疾病</v>
+        <v>疾病-肠炎病</v>
       </c>
       <c r="G405">
         <v>144</v>
@@ -20666,7 +20666,7 @@
         <v>3224</v>
       </c>
       <c r="F406" t="str">
-        <v>水质异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G406">
         <v>158</v>
@@ -20716,7 +20716,7 @@
         <v>3277</v>
       </c>
       <c r="F407" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G407">
         <v>130</v>
@@ -20766,7 +20766,7 @@
         <v>7044</v>
       </c>
       <c r="F408" t="str">
-        <v>疾病</v>
+        <v>疾病-水霉病</v>
       </c>
       <c r="G408">
         <v>126</v>
@@ -20816,7 +20816,7 @@
         <v>6685</v>
       </c>
       <c r="F409" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G409">
         <v>177</v>
@@ -20866,7 +20866,7 @@
         <v>5353</v>
       </c>
       <c r="F410" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G410">
         <v>161</v>
@@ -20916,7 +20916,7 @@
         <v>4980</v>
       </c>
       <c r="F411" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G411">
         <v>173</v>
@@ -20966,7 +20966,7 @@
         <v>4661</v>
       </c>
       <c r="F412" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G412">
         <v>140</v>
@@ -21016,7 +21016,7 @@
         <v>4410</v>
       </c>
       <c r="F413" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G413">
         <v>139</v>
@@ -21066,7 +21066,7 @@
         <v>3330</v>
       </c>
       <c r="F414" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G414">
         <v>176</v>
@@ -21116,7 +21116,7 @@
         <v>7454</v>
       </c>
       <c r="F415" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G415">
         <v>151</v>
@@ -21166,7 +21166,7 @@
         <v>4448</v>
       </c>
       <c r="F416" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G416">
         <v>161</v>
@@ -21216,7 +21216,7 @@
         <v>6788</v>
       </c>
       <c r="F417" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G417">
         <v>179</v>
@@ -21266,7 +21266,7 @@
         <v>4203</v>
       </c>
       <c r="F418" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G418">
         <v>120</v>
@@ -21316,7 +21316,7 @@
         <v>4946</v>
       </c>
       <c r="F419" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G419">
         <v>134</v>
@@ -21366,7 +21366,7 @@
         <v>7461</v>
       </c>
       <c r="F420" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G420">
         <v>156</v>
@@ -21416,7 +21416,7 @@
         <v>3457</v>
       </c>
       <c r="F421" t="str">
-        <v>疾病</v>
+        <v>疾病-水霉病</v>
       </c>
       <c r="G421">
         <v>91</v>
@@ -21466,7 +21466,7 @@
         <v>7003</v>
       </c>
       <c r="F422" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G422">
         <v>148</v>
@@ -21516,7 +21516,7 @@
         <v>5848</v>
       </c>
       <c r="F423" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G423">
         <v>140</v>
@@ -21566,7 +21566,7 @@
         <v>3835</v>
       </c>
       <c r="F424" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G424">
         <v>142</v>
@@ -21616,7 +21616,7 @@
         <v>6345</v>
       </c>
       <c r="F425" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G425">
         <v>139</v>
@@ -21666,7 +21666,7 @@
         <v>5144</v>
       </c>
       <c r="F426" t="str">
-        <v>疾病</v>
+        <v>疾病-指环虫感染</v>
       </c>
       <c r="G426">
         <v>157</v>
@@ -21716,7 +21716,7 @@
         <v>6841</v>
       </c>
       <c r="F427" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G427">
         <v>177</v>
@@ -21766,7 +21766,7 @@
         <v>5479</v>
       </c>
       <c r="F428" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G428">
         <v>156</v>
@@ -21816,7 +21816,7 @@
         <v>6442</v>
       </c>
       <c r="F429" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G429">
         <v>152</v>
@@ -21866,7 +21866,7 @@
         <v>4727</v>
       </c>
       <c r="F430" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G430">
         <v>120</v>
@@ -21916,7 +21916,7 @@
         <v>6866</v>
       </c>
       <c r="F431" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G431">
         <v>154</v>
@@ -21966,7 +21966,7 @@
         <v>7758</v>
       </c>
       <c r="F432" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G432">
         <v>160</v>
@@ -22016,7 +22016,7 @@
         <v>6435</v>
       </c>
       <c r="F433" t="str">
-        <v>疾病</v>
+        <v>疾病-车轮虫感染</v>
       </c>
       <c r="G433">
         <v>133</v>
@@ -22066,7 +22066,7 @@
         <v>7048</v>
       </c>
       <c r="F434" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-霉变饲料</v>
       </c>
       <c r="G434">
         <v>153</v>
@@ -22116,7 +22116,7 @@
         <v>4261</v>
       </c>
       <c r="F435" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G435">
         <v>173</v>
@@ -22166,7 +22166,7 @@
         <v>3688</v>
       </c>
       <c r="F436" t="str">
-        <v>疾病</v>
+        <v>疾病-指环虫感染</v>
       </c>
       <c r="G436">
         <v>127</v>
@@ -22216,7 +22216,7 @@
         <v>6346</v>
       </c>
       <c r="F437" t="str">
-        <v>水质异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G437">
         <v>180</v>
@@ -22266,7 +22266,7 @@
         <v>7216</v>
       </c>
       <c r="F438" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G438">
         <v>145</v>
@@ -22316,7 +22316,7 @@
         <v>3640</v>
       </c>
       <c r="F439" t="str">
-        <v>水质异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G439">
         <v>156</v>
@@ -22366,7 +22366,7 @@
         <v>4685</v>
       </c>
       <c r="F440" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G440">
         <v>178</v>
@@ -22416,7 +22416,7 @@
         <v>4045</v>
       </c>
       <c r="F441" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G441">
         <v>97</v>
@@ -22466,7 +22466,7 @@
         <v>6629</v>
       </c>
       <c r="F442" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G442">
         <v>121</v>
@@ -22516,7 +22516,7 @@
         <v>6663</v>
       </c>
       <c r="F443" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G443">
         <v>125</v>
@@ -22566,7 +22566,7 @@
         <v>6135</v>
       </c>
       <c r="F444" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G444">
         <v>163</v>
@@ -22616,7 +22616,7 @@
         <v>6115</v>
       </c>
       <c r="F445" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G445">
         <v>111</v>
@@ -22666,7 +22666,7 @@
         <v>6350</v>
       </c>
       <c r="F446" t="str">
-        <v>疾病</v>
+        <v>疾病-水霉病</v>
       </c>
       <c r="G446">
         <v>143</v>
@@ -22716,7 +22716,7 @@
         <v>3141</v>
       </c>
       <c r="F447" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G447">
         <v>123</v>
@@ -22766,7 +22766,7 @@
         <v>4107</v>
       </c>
       <c r="F448" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G448">
         <v>96</v>
@@ -22816,7 +22816,7 @@
         <v>5303</v>
       </c>
       <c r="F449" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G449">
         <v>120</v>
@@ -22866,7 +22866,7 @@
         <v>6756</v>
       </c>
       <c r="F450" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G450">
         <v>106</v>
@@ -22916,7 +22916,7 @@
         <v>7296</v>
       </c>
       <c r="F451" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G451">
         <v>143</v>
@@ -22966,7 +22966,7 @@
         <v>5092</v>
       </c>
       <c r="F452" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G452">
         <v>97</v>
@@ -23016,7 +23016,7 @@
         <v>4404</v>
       </c>
       <c r="F453" t="str">
-        <v>疾病</v>
+        <v>疾病-细菌性烂鳃病</v>
       </c>
       <c r="G453">
         <v>94</v>
@@ -23066,7 +23066,7 @@
         <v>5261</v>
       </c>
       <c r="F454" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G454">
         <v>153</v>
@@ -23116,7 +23116,7 @@
         <v>6882</v>
       </c>
       <c r="F455" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G455">
         <v>142</v>
@@ -23166,7 +23166,7 @@
         <v>3818</v>
       </c>
       <c r="F456" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G456">
         <v>97</v>
@@ -23216,7 +23216,7 @@
         <v>3496</v>
       </c>
       <c r="F457" t="str">
-        <v>疾病</v>
+        <v>疾病-肠炎病</v>
       </c>
       <c r="G457">
         <v>119</v>
@@ -23266,7 +23266,7 @@
         <v>5793</v>
       </c>
       <c r="F458" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G458">
         <v>132</v>
@@ -23316,7 +23316,7 @@
         <v>7056</v>
       </c>
       <c r="F459" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G459">
         <v>136</v>
@@ -23366,7 +23366,7 @@
         <v>5682</v>
       </c>
       <c r="F460" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G460">
         <v>127</v>
@@ -23416,7 +23416,7 @@
         <v>4838</v>
       </c>
       <c r="F461" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G461">
         <v>95</v>
@@ -23466,7 +23466,7 @@
         <v>3710</v>
       </c>
       <c r="F462" t="str">
-        <v>疾病</v>
+        <v>疾病-水霉病</v>
       </c>
       <c r="G462">
         <v>161</v>
@@ -23516,7 +23516,7 @@
         <v>6137</v>
       </c>
       <c r="F463" t="str">
-        <v>疾病</v>
+        <v>疾病-车轮虫感染</v>
       </c>
       <c r="G463">
         <v>153</v>
@@ -23566,7 +23566,7 @@
         <v>7651</v>
       </c>
       <c r="F464" t="str">
-        <v>疾病</v>
+        <v>疾病-水霉病</v>
       </c>
       <c r="G464">
         <v>173</v>
@@ -23616,7 +23616,7 @@
         <v>3242</v>
       </c>
       <c r="F465" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G465">
         <v>129</v>
@@ -23666,7 +23666,7 @@
         <v>6794</v>
       </c>
       <c r="F466" t="str">
-        <v>疾病</v>
+        <v>疾病-肠炎病</v>
       </c>
       <c r="G466">
         <v>142</v>
@@ -23716,7 +23716,7 @@
         <v>3504</v>
       </c>
       <c r="F467" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G467">
         <v>97</v>
@@ -23766,7 +23766,7 @@
         <v>6857</v>
       </c>
       <c r="F468" t="str">
-        <v>水质异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G468">
         <v>132</v>
@@ -23816,7 +23816,7 @@
         <v>3141</v>
       </c>
       <c r="F469" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G469">
         <v>101</v>
@@ -23866,7 +23866,7 @@
         <v>3672</v>
       </c>
       <c r="F470" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G470">
         <v>107</v>
@@ -23916,7 +23916,7 @@
         <v>6207</v>
       </c>
       <c r="F471" t="str">
-        <v>疾病</v>
+        <v>疾病-细菌性烂鳃病</v>
       </c>
       <c r="G471">
         <v>143</v>
@@ -23966,7 +23966,7 @@
         <v>4328</v>
       </c>
       <c r="F472" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G472">
         <v>172</v>
@@ -24016,7 +24016,7 @@
         <v>2948</v>
       </c>
       <c r="F473" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G473">
         <v>110</v>
@@ -24066,7 +24066,7 @@
         <v>3272</v>
       </c>
       <c r="F474" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G474">
         <v>171</v>
@@ -24116,7 +24116,7 @@
         <v>3423</v>
       </c>
       <c r="F475" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G475">
         <v>171</v>
@@ -24166,7 +24166,7 @@
         <v>4028</v>
       </c>
       <c r="F476" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G476">
         <v>155</v>
@@ -24216,7 +24216,7 @@
         <v>3073</v>
       </c>
       <c r="F477" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G477">
         <v>144</v>
@@ -24266,7 +24266,7 @@
         <v>6345</v>
       </c>
       <c r="F478" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G478">
         <v>107</v>
@@ -24316,7 +24316,7 @@
         <v>6316</v>
       </c>
       <c r="F479" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G479">
         <v>101</v>
@@ -24366,7 +24366,7 @@
         <v>6991</v>
       </c>
       <c r="F480" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G480">
         <v>103</v>
@@ -24416,7 +24416,7 @@
         <v>4613</v>
       </c>
       <c r="F481" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G481">
         <v>167</v>
@@ -24466,7 +24466,7 @@
         <v>3223</v>
       </c>
       <c r="F482" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G482">
         <v>108</v>
@@ -24516,7 +24516,7 @@
         <v>4948</v>
       </c>
       <c r="F483" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G483">
         <v>139</v>
@@ -24566,7 +24566,7 @@
         <v>2950</v>
       </c>
       <c r="F484" t="str">
-        <v>水质异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G484">
         <v>153</v>
@@ -24616,7 +24616,7 @@
         <v>7755</v>
       </c>
       <c r="F485" t="str">
-        <v>水质异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G485">
         <v>166</v>
@@ -24666,7 +24666,7 @@
         <v>6558</v>
       </c>
       <c r="F486" t="str">
-        <v>水质异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G486">
         <v>108</v>
@@ -24716,7 +24716,7 @@
         <v>5380</v>
       </c>
       <c r="F487" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G487">
         <v>113</v>
@@ -24766,7 +24766,7 @@
         <v>7402</v>
       </c>
       <c r="F488" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G488">
         <v>153</v>
@@ -24816,7 +24816,7 @@
         <v>3312</v>
       </c>
       <c r="F489" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G489">
         <v>141</v>
@@ -24866,7 +24866,7 @@
         <v>5923</v>
       </c>
       <c r="F490" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G490">
         <v>180</v>
@@ -24916,7 +24916,7 @@
         <v>3649</v>
       </c>
       <c r="F491" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G491">
         <v>114</v>
@@ -24966,7 +24966,7 @@
         <v>3154</v>
       </c>
       <c r="F492" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G492">
         <v>120</v>
@@ -25016,7 +25016,7 @@
         <v>6169</v>
       </c>
       <c r="F493" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G493">
         <v>120</v>
@@ -25066,7 +25066,7 @@
         <v>4409</v>
       </c>
       <c r="F494" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G494">
         <v>125</v>
@@ -25116,7 +25116,7 @@
         <v>3848</v>
       </c>
       <c r="F495" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G495">
         <v>117</v>
@@ -25166,7 +25166,7 @@
         <v>3498</v>
       </c>
       <c r="F496" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G496">
         <v>110</v>
@@ -25216,7 +25216,7 @@
         <v>7269</v>
       </c>
       <c r="F497" t="str">
-        <v>水质异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G497">
         <v>150</v>
@@ -25266,7 +25266,7 @@
         <v>3241</v>
       </c>
       <c r="F498" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G498">
         <v>125</v>
@@ -25316,7 +25316,7 @@
         <v>4358</v>
       </c>
       <c r="F499" t="str">
-        <v>水质异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G499">
         <v>177</v>
@@ -25366,7 +25366,7 @@
         <v>3663</v>
       </c>
       <c r="F500" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G500">
         <v>125</v>
@@ -25416,7 +25416,7 @@
         <v>4746</v>
       </c>
       <c r="F501" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G501">
         <v>100</v>
@@ -25466,7 +25466,7 @@
         <v>6355</v>
       </c>
       <c r="F502" t="str">
-        <v>水质异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G502">
         <v>141</v>
@@ -25516,7 +25516,7 @@
         <v>2842</v>
       </c>
       <c r="F503" t="str">
-        <v>水质异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G503">
         <v>98</v>
@@ -25566,7 +25566,7 @@
         <v>6843</v>
       </c>
       <c r="F504" t="str">
-        <v>密度过高</v>
+        <v>密度过高-缺氧窒息</v>
       </c>
       <c r="G504">
         <v>162</v>
@@ -25616,7 +25616,7 @@
         <v>3302</v>
       </c>
       <c r="F505" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G505">
         <v>163</v>
@@ -25666,7 +25666,7 @@
         <v>4773</v>
       </c>
       <c r="F506" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G506">
         <v>177</v>
@@ -25716,7 +25716,7 @@
         <v>5114</v>
       </c>
       <c r="F507" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G507">
         <v>91</v>
@@ -25766,7 +25766,7 @@
         <v>6559</v>
       </c>
       <c r="F508" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G508">
         <v>113</v>
@@ -25816,7 +25816,7 @@
         <v>7048</v>
       </c>
       <c r="F509" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G509">
         <v>152</v>
@@ -25866,7 +25866,7 @@
         <v>5640</v>
       </c>
       <c r="F510" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G510">
         <v>131</v>
@@ -25916,7 +25916,7 @@
         <v>6729</v>
       </c>
       <c r="F511" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G511">
         <v>97</v>
@@ -25966,7 +25966,7 @@
         <v>6777</v>
       </c>
       <c r="F512" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G512">
         <v>119</v>
@@ -26016,7 +26016,7 @@
         <v>6293</v>
       </c>
       <c r="F513" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G513">
         <v>130</v>
@@ -26066,7 +26066,7 @@
         <v>5634</v>
       </c>
       <c r="F514" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G514">
         <v>152</v>
@@ -26116,7 +26116,7 @@
         <v>7269</v>
       </c>
       <c r="F515" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G515">
         <v>113</v>
@@ -26166,7 +26166,7 @@
         <v>3651</v>
       </c>
       <c r="F516" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G516">
         <v>180</v>
@@ -26216,7 +26216,7 @@
         <v>6824</v>
       </c>
       <c r="F517" t="str">
-        <v>水质异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G517">
         <v>99</v>
@@ -26266,7 +26266,7 @@
         <v>5023</v>
       </c>
       <c r="F518" t="str">
-        <v>疾病</v>
+        <v>疾病-肠炎病</v>
       </c>
       <c r="G518">
         <v>147</v>
@@ -26316,7 +26316,7 @@
         <v>6934</v>
       </c>
       <c r="F519" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G519">
         <v>113</v>
@@ -26366,7 +26366,7 @@
         <v>5315</v>
       </c>
       <c r="F520" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G520">
         <v>158</v>
@@ -26416,7 +26416,7 @@
         <v>3388</v>
       </c>
       <c r="F521" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G521">
         <v>111</v>
@@ -26466,7 +26466,7 @@
         <v>4946</v>
       </c>
       <c r="F522" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-霉变饲料</v>
       </c>
       <c r="G522">
         <v>136</v>
@@ -26516,7 +26516,7 @@
         <v>5548</v>
       </c>
       <c r="F523" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G523">
         <v>168</v>
@@ -26566,7 +26566,7 @@
         <v>6850</v>
       </c>
       <c r="F524" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G524">
         <v>136</v>
@@ -26616,7 +26616,7 @@
         <v>4859</v>
       </c>
       <c r="F525" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G525">
         <v>169</v>
@@ -26666,7 +26666,7 @@
         <v>6014</v>
       </c>
       <c r="F526" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G526">
         <v>130</v>
@@ -26716,7 +26716,7 @@
         <v>7463</v>
       </c>
       <c r="F527" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G527">
         <v>174</v>
@@ -26766,7 +26766,7 @@
         <v>4145</v>
       </c>
       <c r="F528" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G528">
         <v>138</v>
@@ -26816,7 +26816,7 @@
         <v>4232</v>
       </c>
       <c r="F529" t="str">
-        <v>水质异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G529">
         <v>155</v>
@@ -26866,7 +26866,7 @@
         <v>7447</v>
       </c>
       <c r="F530" t="str">
-        <v>水质异常</v>
+        <v>水质异常-亚硝酸盐超标</v>
       </c>
       <c r="G530">
         <v>158</v>
@@ -26916,7 +26916,7 @@
         <v>6180</v>
       </c>
       <c r="F531" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G531">
         <v>97</v>
@@ -26966,7 +26966,7 @@
         <v>6919</v>
       </c>
       <c r="F532" t="str">
-        <v>疾病</v>
+        <v>疾病-肠炎病</v>
       </c>
       <c r="G532">
         <v>99</v>
@@ -27016,7 +27016,7 @@
         <v>6992</v>
       </c>
       <c r="F533" t="str">
-        <v>水质异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G533">
         <v>118</v>
@@ -27066,7 +27066,7 @@
         <v>3764</v>
       </c>
       <c r="F534" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G534">
         <v>135</v>
@@ -27116,7 +27116,7 @@
         <v>5670</v>
       </c>
       <c r="F535" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G535">
         <v>166</v>
@@ -27166,7 +27166,7 @@
         <v>5119</v>
       </c>
       <c r="F536" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G536">
         <v>92</v>
@@ -27216,7 +27216,7 @@
         <v>5947</v>
       </c>
       <c r="F537" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G537">
         <v>127</v>
@@ -27266,7 +27266,7 @@
         <v>2938</v>
       </c>
       <c r="F538" t="str">
-        <v>疾病</v>
+        <v>疾病-车轮虫感染</v>
       </c>
       <c r="G538">
         <v>119</v>
@@ -27316,7 +27316,7 @@
         <v>4565</v>
       </c>
       <c r="F539" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G539">
         <v>175</v>
@@ -27366,7 +27366,7 @@
         <v>3174</v>
       </c>
       <c r="F540" t="str">
-        <v>水质异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G540">
         <v>116</v>
@@ -27416,7 +27416,7 @@
         <v>2980</v>
       </c>
       <c r="F541" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-氨氮超标</v>
       </c>
       <c r="G541">
         <v>152</v>
@@ -27466,7 +27466,7 @@
         <v>7442</v>
       </c>
       <c r="F542" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-分塘损伤</v>
       </c>
       <c r="G542">
         <v>152</v>
@@ -27516,7 +27516,7 @@
         <v>3190</v>
       </c>
       <c r="F543" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-投喂过量</v>
       </c>
       <c r="G543">
         <v>171</v>
@@ -27566,7 +27566,7 @@
         <v>5026</v>
       </c>
       <c r="F544" t="str">
-        <v>密度过高</v>
+        <v>密度过高-争食受伤</v>
       </c>
       <c r="G544">
         <v>152</v>
@@ -27616,7 +27616,7 @@
         <v>4265</v>
       </c>
       <c r="F545" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G545">
         <v>175</v>
@@ -27666,7 +27666,7 @@
         <v>6894</v>
       </c>
       <c r="F546" t="str">
-        <v>pH值异常</v>
+        <v>水质异常-溶氧不足</v>
       </c>
       <c r="G546">
         <v>92</v>
@@ -27716,7 +27716,7 @@
         <v>3289</v>
       </c>
       <c r="F547" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-捕捞应激</v>
       </c>
       <c r="G547">
         <v>101</v>
@@ -27766,7 +27766,7 @@
         <v>7017</v>
       </c>
       <c r="F548" t="str">
-        <v>水质异常</v>
+        <v>水质异常-pH值偏离</v>
       </c>
       <c r="G548">
         <v>150</v>
@@ -27816,7 +27816,7 @@
         <v>5581</v>
       </c>
       <c r="F549" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G549">
         <v>132</v>
@@ -27866,7 +27866,7 @@
         <v>3062</v>
       </c>
       <c r="F550" t="str">
-        <v>操作损伤</v>
+        <v>操作损伤-运输损伤</v>
       </c>
       <c r="G550">
         <v>119</v>
@@ -27916,7 +27916,7 @@
         <v>6506</v>
       </c>
       <c r="F551" t="str">
-        <v>饲料问题</v>
+        <v>饲料问题-营养不良</v>
       </c>
       <c r="G551">
         <v>115</v>
